--- a/uploads/harmonized_upload.xlsx
+++ b/uploads/harmonized_upload.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janhavi.thukkaram\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7536DD33-C2E0-4AE4-AEEE-C1DF943D4824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60546C51-A55D-4F81-A524-94A30DE80264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0D8D18B6-D960-4EF5-96D0-EAFE98B1038D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="231">
   <si>
     <t>Sample_ID</t>
   </si>
@@ -718,6 +718,15 @@
   </si>
   <si>
     <t>pGEX-4T-1</t>
+  </si>
+  <si>
+    <t>CRO-Name</t>
+  </si>
+  <si>
+    <t>CRO-A</t>
+  </si>
+  <si>
+    <t>CRO-B</t>
   </si>
 </sst>
 </file>
@@ -746,7 +755,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -801,6 +810,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -814,7 +829,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -827,6 +842,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1161,2942 +1177,3005 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A25361C4-28D8-480E-AD9F-29C9F84CF962}">
-  <dimension ref="A1:AR32"/>
+  <dimension ref="A1:AS32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="89.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.08984375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.08984375" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="89.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.08984375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="14.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AG1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AH1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="7" t="s">
+      <c r="AI1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AJ1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="7" t="s">
+      <c r="AK1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="7" t="s">
+      <c r="AL1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="7" t="s">
+      <c r="AM1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="8" t="s">
+      <c r="AN1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="8" t="s">
+      <c r="AO1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="8" t="s">
+      <c r="AP1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="8" t="s">
+      <c r="AQ1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="8" t="s">
+      <c r="AR1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="8" t="s">
+      <c r="AS1" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="9">
+      <c r="G2" s="9">
         <v>3.7</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="I2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>198</v>
       </c>
-      <c r="L2" s="9">
+      <c r="M2" s="9">
         <v>701</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>3.21</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="O2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="Q2" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="R2" s="9">
         <v>1401</v>
       </c>
-      <c r="R2" s="9">
+      <c r="S2" s="9">
         <v>48.2</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="T2" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="U2" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="V2" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="V2" s="10">
+      <c r="W2" s="10">
         <v>45301</v>
       </c>
-      <c r="W2" s="10">
+      <c r="X2" s="10">
         <v>46032</v>
       </c>
-      <c r="X2" s="9" t="s">
+      <c r="Y2" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y2" s="9">
+      <c r="Z2" s="9">
         <v>98.5</v>
       </c>
-      <c r="Z2" s="9" t="s">
+      <c r="AA2" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA2" s="9" t="s">
+      <c r="AB2" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="AB2" s="9" t="s">
+      <c r="AC2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC2" s="9" t="s">
+      <c r="AD2" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="AD2" s="9">
+      <c r="AE2" s="9">
         <v>6</v>
       </c>
-      <c r="AE2" s="9">
+      <c r="AF2" s="9">
         <v>2</v>
       </c>
-      <c r="AF2" s="9" t="s">
+      <c r="AG2" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="AG2" s="9" t="s">
+      <c r="AH2" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AH2" s="9" t="s">
+      <c r="AI2" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI2" s="9">
+      <c r="AJ2" s="9">
         <v>0.71</v>
       </c>
-      <c r="AJ2" s="9" t="s">
+      <c r="AK2" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK2" s="9">
+      <c r="AL2" s="9">
         <v>1</v>
       </c>
-      <c r="AL2" s="9" t="s">
+      <c r="AM2" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM2" s="9" t="s">
+      <c r="AN2" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="AN2" s="9" t="s">
+      <c r="AO2" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AO2" s="9" t="s">
+      <c r="AP2" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP2" s="9" t="s">
+      <c r="AQ2" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AQ2" s="9" t="s">
+      <c r="AR2" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="AR2" s="10">
+      <c r="AS2" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="9">
+      <c r="G3" s="9">
         <v>3.9</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="L3" s="9">
+      <c r="M3" s="9">
         <v>702</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>2.87</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="O3" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="P3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="Q3" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="Q3" s="9">
+      <c r="R3" s="9">
         <v>1402</v>
       </c>
-      <c r="R3" s="9">
+      <c r="S3" s="9">
         <v>51.4</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="T3" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="U3" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="V3" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="V3" s="10">
+      <c r="W3" s="10">
         <v>45301</v>
       </c>
-      <c r="W3" s="10">
+      <c r="X3" s="10">
         <v>46032</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="Y3" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y3" s="9">
+      <c r="Z3" s="9">
         <v>97.8</v>
       </c>
-      <c r="Z3" s="9" t="s">
+      <c r="AA3" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA3" s="9" t="s">
+      <c r="AB3" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="AB3" s="9" t="s">
+      <c r="AC3" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC3" s="9" t="s">
+      <c r="AD3" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="AD3" s="9">
+      <c r="AE3" s="9">
         <v>7</v>
       </c>
-      <c r="AE3" s="9">
+      <c r="AF3" s="9">
         <v>2</v>
       </c>
-      <c r="AF3" s="9" t="s">
+      <c r="AG3" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="AG3" s="9" t="s">
+      <c r="AH3" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AH3" s="9" t="s">
+      <c r="AI3" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI3" s="9">
+      <c r="AJ3" s="9">
         <v>0.72</v>
       </c>
-      <c r="AJ3" s="9" t="s">
+      <c r="AK3" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK3" s="9">
+      <c r="AL3" s="9">
         <v>1</v>
       </c>
-      <c r="AL3" s="9" t="s">
+      <c r="AM3" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM3" s="9" t="s">
+      <c r="AN3" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AN3" s="9" t="s">
+      <c r="AO3" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AO3" s="9" t="s">
+      <c r="AP3" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP3" s="9" t="s">
+      <c r="AQ3" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="AQ3" s="9">
+      <c r="AR3" s="9">
         <v>1260</v>
       </c>
-      <c r="AR3" s="10">
+      <c r="AS3" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="9">
+      <c r="G4" s="9">
         <v>3.5</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="I4" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="J4" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="L4" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="L4" s="9">
+      <c r="M4" s="9">
         <v>703</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>4.1500000000000004</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="O4" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="P4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="Q4" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="Q4" s="9">
+      <c r="R4" s="9">
         <v>1403</v>
       </c>
-      <c r="R4" s="9">
+      <c r="S4" s="9">
         <v>46.7</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="T4" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="T4" s="9" t="s">
+      <c r="U4" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="U4" s="9" t="s">
+      <c r="V4" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="V4" s="10">
+      <c r="W4" s="10">
         <v>45301</v>
       </c>
-      <c r="W4" s="10">
+      <c r="X4" s="10">
         <v>46032</v>
       </c>
-      <c r="X4" s="9" t="s">
+      <c r="Y4" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y4" s="9">
+      <c r="Z4" s="9">
         <v>99.1</v>
       </c>
-      <c r="Z4" s="9" t="s">
+      <c r="AA4" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA4" s="9" t="s">
+      <c r="AB4" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="AB4" s="9" t="s">
+      <c r="AC4" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC4" s="9" t="s">
+      <c r="AD4" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="AD4" s="9">
+      <c r="AE4" s="9">
         <v>8</v>
       </c>
-      <c r="AE4" s="9">
+      <c r="AF4" s="9">
         <v>2</v>
       </c>
-      <c r="AF4" s="9" t="s">
+      <c r="AG4" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="AG4" s="9" t="s">
+      <c r="AH4" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AH4" s="9" t="s">
+      <c r="AI4" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI4" s="9">
+      <c r="AJ4" s="9">
         <v>0.73</v>
       </c>
-      <c r="AJ4" s="9" t="s">
+      <c r="AK4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK4" s="9">
+      <c r="AL4" s="9">
         <v>1</v>
       </c>
-      <c r="AL4" s="9" t="s">
+      <c r="AM4" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM4" s="9" t="s">
+      <c r="AN4" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="AN4" s="9" t="s">
+      <c r="AO4" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="AO4" s="9" t="s">
+      <c r="AP4" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP4" s="9" t="s">
+      <c r="AQ4" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="AQ4" s="9" t="s">
+      <c r="AR4" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="AR4" s="10">
+      <c r="AS4" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="9">
+      <c r="G5" s="9">
         <v>3.7</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="I5" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="J5" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="L5" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="L5" s="9">
+      <c r="M5" s="9">
         <v>704</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>3.76</v>
       </c>
-      <c r="N5" s="9" t="s">
+      <c r="O5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="P5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="Q5" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="Q5" s="9">
+      <c r="R5" s="9">
         <v>1404</v>
       </c>
-      <c r="R5" s="9">
+      <c r="S5" s="9">
         <v>52.1</v>
       </c>
-      <c r="S5" s="9" t="s">
+      <c r="T5" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T5" s="9" t="s">
+      <c r="U5" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="U5" s="9" t="s">
+      <c r="V5" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="V5" s="10">
+      <c r="W5" s="10">
         <v>45301</v>
       </c>
-      <c r="W5" s="10">
+      <c r="X5" s="10">
         <v>46032</v>
       </c>
-      <c r="X5" s="9" t="s">
+      <c r="Y5" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y5" s="9">
+      <c r="Z5" s="9">
         <v>96.9</v>
       </c>
-      <c r="Z5" s="9" t="s">
+      <c r="AA5" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA5" s="9" t="s">
+      <c r="AB5" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="AB5" s="9" t="s">
+      <c r="AC5" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC5" s="9" t="s">
+      <c r="AD5" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AD5" s="9">
+      <c r="AE5" s="9">
         <v>9</v>
       </c>
-      <c r="AE5" s="9">
+      <c r="AF5" s="9">
         <v>2</v>
       </c>
-      <c r="AF5" s="9" t="s">
+      <c r="AG5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="AG5" s="9" t="s">
+      <c r="AH5" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AH5" s="9" t="s">
+      <c r="AI5" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI5" s="9">
+      <c r="AJ5" s="9">
         <v>0.74</v>
       </c>
-      <c r="AJ5" s="9" t="s">
+      <c r="AK5" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK5" s="9">
+      <c r="AL5" s="9">
         <v>1</v>
       </c>
-      <c r="AL5" s="9" t="s">
+      <c r="AM5" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM5" s="9" t="s">
+      <c r="AN5" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="AN5" s="9" t="s">
+      <c r="AO5" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AO5" s="9" t="s">
+      <c r="AP5" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP5" s="9" t="s">
+      <c r="AQ5" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AQ5" s="9" t="s">
+      <c r="AR5" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="AR5" s="10">
+      <c r="AS5" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="9">
+      <c r="G6" s="9">
         <v>3.9</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="I6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="J6" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="L6" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L6" s="9">
+      <c r="M6" s="9">
         <v>705</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>4.0199999999999996</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="O6" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="P6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="Q6" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="Q6" s="9">
+      <c r="R6" s="9">
         <v>1405</v>
       </c>
-      <c r="R6" s="9">
+      <c r="S6" s="9">
         <v>49.8</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="T6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T6" s="9" t="s">
+      <c r="U6" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="U6" s="9" t="s">
+      <c r="V6" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="V6" s="10">
+      <c r="W6" s="10">
         <v>45301</v>
       </c>
-      <c r="W6" s="10">
+      <c r="X6" s="10">
         <v>46032</v>
       </c>
-      <c r="X6" s="9" t="s">
+      <c r="Y6" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y6" s="9">
+      <c r="Z6" s="9">
         <v>98.2</v>
       </c>
-      <c r="Z6" s="9" t="s">
+      <c r="AA6" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA6" s="9" t="s">
+      <c r="AB6" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="AB6" s="9" t="s">
+      <c r="AC6" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC6" s="9" t="s">
+      <c r="AD6" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="AD6" s="9">
+      <c r="AE6" s="9">
         <v>5</v>
       </c>
-      <c r="AE6" s="9">
+      <c r="AF6" s="9">
         <v>2</v>
       </c>
-      <c r="AF6" s="9" t="s">
+      <c r="AG6" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AG6" s="9" t="s">
+      <c r="AH6" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AH6" s="9" t="s">
+      <c r="AI6" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI6" s="9">
+      <c r="AJ6" s="9">
         <v>0.75</v>
       </c>
-      <c r="AJ6" s="9" t="s">
+      <c r="AK6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK6" s="9">
+      <c r="AL6" s="9">
         <v>1</v>
       </c>
-      <c r="AL6" s="9" t="s">
+      <c r="AM6" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM6" s="9" t="s">
+      <c r="AN6" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AN6" s="9" t="s">
+      <c r="AO6" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AO6" s="9" t="s">
+      <c r="AP6" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP6" s="9" t="s">
+      <c r="AQ6" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="AQ6" s="9">
+      <c r="AR6" s="9">
         <v>1260</v>
       </c>
-      <c r="AR6" s="10">
+      <c r="AS6" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="C7" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="9">
+      <c r="G7" s="9">
         <v>3.5</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="I7" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="J7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="K7" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="L7" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="L7" s="9">
+      <c r="M7" s="9">
         <v>706</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>1.95</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="O7" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="P7" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P7" s="9" t="s">
+      <c r="Q7" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="Q7" s="9">
+      <c r="R7" s="9">
         <v>1406</v>
       </c>
-      <c r="R7" s="9">
+      <c r="S7" s="9">
         <v>47.5</v>
       </c>
-      <c r="S7" s="9" t="s">
+      <c r="T7" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="T7" s="9" t="s">
+      <c r="U7" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="U7" s="9" t="s">
+      <c r="V7" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="V7" s="10">
+      <c r="W7" s="10">
         <v>45301</v>
       </c>
-      <c r="W7" s="10">
+      <c r="X7" s="10">
         <v>46032</v>
       </c>
-      <c r="X7" s="9" t="s">
+      <c r="Y7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y7" s="9">
+      <c r="Z7" s="9">
         <v>97.4</v>
       </c>
-      <c r="Z7" s="9" t="s">
+      <c r="AA7" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA7" s="9" t="s">
+      <c r="AB7" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="AB7" s="9" t="s">
+      <c r="AC7" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC7" s="9" t="s">
+      <c r="AD7" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="AD7" s="9">
+      <c r="AE7" s="9">
         <v>6</v>
       </c>
-      <c r="AE7" s="9">
+      <c r="AF7" s="9">
         <v>2</v>
       </c>
-      <c r="AF7" s="9" t="s">
+      <c r="AG7" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="AG7" s="9" t="s">
+      <c r="AH7" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AH7" s="9" t="s">
+      <c r="AI7" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI7" s="9">
+      <c r="AJ7" s="9">
         <v>0.76</v>
       </c>
-      <c r="AJ7" s="9" t="s">
+      <c r="AK7" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK7" s="9">
+      <c r="AL7" s="9">
         <v>1</v>
       </c>
-      <c r="AL7" s="9" t="s">
+      <c r="AM7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM7" s="9" t="s">
+      <c r="AN7" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="AN7" s="9" t="s">
+      <c r="AO7" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="AO7" s="9" t="s">
+      <c r="AP7" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP7" s="9" t="s">
+      <c r="AQ7" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="AQ7" s="9" t="s">
+      <c r="AR7" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="AR7" s="10">
+      <c r="AS7" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="D8" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="9">
+      <c r="G8" s="9">
         <v>3.7</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="I8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="J8" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="K8" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="L8" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="L8" s="9">
+      <c r="M8" s="9">
         <v>707</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>2.48</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="P8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="Q8" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="Q8" s="9">
+      <c r="R8" s="9">
         <v>1407</v>
       </c>
-      <c r="R8" s="9">
+      <c r="S8" s="9">
         <v>50.3</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="T8" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T8" s="9" t="s">
+      <c r="U8" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="U8" s="9" t="s">
+      <c r="V8" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="V8" s="10">
+      <c r="W8" s="10">
         <v>45301</v>
       </c>
-      <c r="W8" s="10">
+      <c r="X8" s="10">
         <v>46032</v>
       </c>
-      <c r="X8" s="9" t="s">
+      <c r="Y8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y8" s="9">
+      <c r="Z8" s="9">
         <v>99</v>
       </c>
-      <c r="Z8" s="9" t="s">
+      <c r="AA8" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA8" s="9" t="s">
+      <c r="AB8" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="AB8" s="9" t="s">
+      <c r="AC8" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC8" s="9" t="s">
+      <c r="AD8" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="AD8" s="9">
+      <c r="AE8" s="9">
         <v>7</v>
       </c>
-      <c r="AE8" s="9">
+      <c r="AF8" s="9">
         <v>2</v>
       </c>
-      <c r="AF8" s="9" t="s">
+      <c r="AG8" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="AG8" s="9" t="s">
+      <c r="AH8" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AH8" s="9" t="s">
+      <c r="AI8" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI8" s="9">
+      <c r="AJ8" s="9">
         <v>0.77</v>
       </c>
-      <c r="AJ8" s="9" t="s">
+      <c r="AK8" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK8" s="9">
+      <c r="AL8" s="9">
         <v>1</v>
       </c>
-      <c r="AL8" s="9" t="s">
+      <c r="AM8" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM8" s="9" t="s">
+      <c r="AN8" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="AN8" s="9" t="s">
+      <c r="AO8" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AO8" s="9" t="s">
+      <c r="AP8" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP8" s="9" t="s">
+      <c r="AQ8" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AQ8" s="9" t="s">
+      <c r="AR8" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="AR8" s="10">
+      <c r="AS8" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="9">
+      <c r="G9" s="9">
         <v>3.9</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="J9" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="K9" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="L9" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="L9" s="9">
+      <c r="M9" s="9">
         <v>708</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>1.72</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="O9" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O9" s="9" t="s">
+      <c r="P9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="Q9" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="Q9" s="9">
+      <c r="R9" s="9">
         <v>1408</v>
       </c>
-      <c r="R9" s="9">
+      <c r="S9" s="9">
         <v>53.2</v>
       </c>
-      <c r="S9" s="9" t="s">
+      <c r="T9" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T9" s="9" t="s">
+      <c r="U9" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="U9" s="9" t="s">
+      <c r="V9" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="V9" s="10">
+      <c r="W9" s="10">
         <v>45301</v>
       </c>
-      <c r="W9" s="10">
+      <c r="X9" s="10">
         <v>46032</v>
       </c>
-      <c r="X9" s="9" t="s">
+      <c r="Y9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y9" s="9">
+      <c r="Z9" s="9">
         <v>98.7</v>
       </c>
-      <c r="Z9" s="9" t="s">
+      <c r="AA9" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA9" s="9" t="s">
+      <c r="AB9" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="AB9" s="9" t="s">
+      <c r="AC9" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC9" s="9" t="s">
+      <c r="AD9" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="AD9" s="9">
+      <c r="AE9" s="9">
         <v>8</v>
       </c>
-      <c r="AE9" s="9">
+      <c r="AF9" s="9">
         <v>2</v>
       </c>
-      <c r="AF9" s="9" t="s">
+      <c r="AG9" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="AG9" s="9" t="s">
+      <c r="AH9" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AH9" s="9" t="s">
+      <c r="AI9" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI9" s="9">
+      <c r="AJ9" s="9">
         <v>0.78</v>
       </c>
-      <c r="AJ9" s="9" t="s">
+      <c r="AK9" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK9" s="9">
+      <c r="AL9" s="9">
         <v>1</v>
       </c>
-      <c r="AL9" s="9" t="s">
+      <c r="AM9" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM9" s="9" t="s">
+      <c r="AN9" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AN9" s="9" t="s">
+      <c r="AO9" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AO9" s="9" t="s">
+      <c r="AP9" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP9" s="9" t="s">
+      <c r="AQ9" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="AQ9" s="9">
+      <c r="AR9" s="9">
         <v>1260</v>
       </c>
-      <c r="AR9" s="10">
+      <c r="AS9" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>230</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="9">
+      <c r="G10" s="9">
         <v>3.5</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="J10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="K10" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="L10" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="L10" s="9">
+      <c r="M10" s="9">
         <v>709</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>2.64</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="O10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="P10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="Q10" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="Q10" s="9">
+      <c r="R10" s="9">
         <v>1409</v>
       </c>
-      <c r="R10" s="9">
+      <c r="S10" s="9">
         <v>45.9</v>
       </c>
-      <c r="S10" s="9" t="s">
+      <c r="T10" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="T10" s="9" t="s">
+      <c r="U10" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="U10" s="9" t="s">
+      <c r="V10" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="V10" s="10">
+      <c r="W10" s="10">
         <v>45301</v>
       </c>
-      <c r="W10" s="10">
+      <c r="X10" s="10">
         <v>46032</v>
       </c>
-      <c r="X10" s="9" t="s">
+      <c r="Y10" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y10" s="9">
+      <c r="Z10" s="9">
         <v>96.5</v>
       </c>
-      <c r="Z10" s="9" t="s">
+      <c r="AA10" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA10" s="9" t="s">
+      <c r="AB10" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="AB10" s="9" t="s">
+      <c r="AC10" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC10" s="9" t="s">
+      <c r="AD10" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="AD10" s="9">
+      <c r="AE10" s="9">
         <v>9</v>
       </c>
-      <c r="AE10" s="9">
+      <c r="AF10" s="9">
         <v>2</v>
       </c>
-      <c r="AF10" s="9" t="s">
+      <c r="AG10" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="AG10" s="9" t="s">
+      <c r="AH10" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AH10" s="9" t="s">
+      <c r="AI10" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI10" s="9">
+      <c r="AJ10" s="9">
         <v>0.79</v>
       </c>
-      <c r="AJ10" s="9" t="s">
+      <c r="AK10" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK10" s="9">
+      <c r="AL10" s="9">
         <v>1</v>
       </c>
-      <c r="AL10" s="9" t="s">
+      <c r="AM10" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM10" s="9" t="s">
+      <c r="AN10" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="AN10" s="9" t="s">
+      <c r="AO10" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="AO10" s="9" t="s">
+      <c r="AP10" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP10" s="9" t="s">
+      <c r="AQ10" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="AQ10" s="9" t="s">
+      <c r="AR10" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="AR10" s="10">
+      <c r="AS10" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="C11" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="9">
+      <c r="G11" s="9">
         <v>3.7</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="H11" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="I11" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="J11" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="K11" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="L11" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="L11" s="9">
+      <c r="M11" s="9">
         <v>710</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>2.91</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="O11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O11" s="9" t="s">
+      <c r="P11" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P11" s="9" t="s">
+      <c r="Q11" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="R11" s="9">
         <v>1410</v>
       </c>
-      <c r="R11" s="9">
+      <c r="S11" s="9">
         <v>48.7</v>
       </c>
-      <c r="S11" s="9" t="s">
+      <c r="T11" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T11" s="9" t="s">
+      <c r="U11" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="U11" s="9" t="s">
+      <c r="V11" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="V11" s="10">
+      <c r="W11" s="10">
         <v>45301</v>
       </c>
-      <c r="W11" s="10">
+      <c r="X11" s="10">
         <v>46032</v>
       </c>
-      <c r="X11" s="9" t="s">
+      <c r="Y11" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y11" s="9">
+      <c r="Z11" s="9">
         <v>97.9</v>
       </c>
-      <c r="Z11" s="9" t="s">
+      <c r="AA11" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA11" s="9" t="s">
+      <c r="AB11" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="AB11" s="9" t="s">
+      <c r="AC11" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC11" s="9" t="s">
+      <c r="AD11" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="AD11" s="9">
+      <c r="AE11" s="9">
         <v>5</v>
       </c>
-      <c r="AE11" s="9">
+      <c r="AF11" s="9">
         <v>2</v>
       </c>
-      <c r="AF11" s="9" t="s">
+      <c r="AG11" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="AG11" s="9" t="s">
+      <c r="AH11" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AH11" s="9" t="s">
+      <c r="AI11" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI11" s="9">
+      <c r="AJ11" s="9">
         <v>0.8</v>
       </c>
-      <c r="AJ11" s="9" t="s">
+      <c r="AK11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK11" s="9">
+      <c r="AL11" s="9">
         <v>1</v>
       </c>
-      <c r="AL11" s="9" t="s">
+      <c r="AM11" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM11" s="9" t="s">
+      <c r="AN11" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="AN11" s="9" t="s">
+      <c r="AO11" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AO11" s="9" t="s">
+      <c r="AP11" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP11" s="9" t="s">
+      <c r="AQ11" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AQ11" s="9" t="s">
+      <c r="AR11" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="AR11" s="10">
+      <c r="AS11" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="9">
+      <c r="G12" s="9">
         <v>3.9</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="I12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="J12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="K12" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="L12" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="L12" s="9">
+      <c r="M12" s="9">
         <v>711</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>2.35</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="O12" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="P12" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P12" s="9" t="s">
+      <c r="Q12" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="R12" s="9">
         <v>1411</v>
       </c>
-      <c r="R12" s="9">
+      <c r="S12" s="9">
         <v>51</v>
       </c>
-      <c r="S12" s="9" t="s">
+      <c r="T12" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T12" s="9" t="s">
+      <c r="U12" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="U12" s="9" t="s">
+      <c r="V12" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="V12" s="10">
+      <c r="W12" s="10">
         <v>45301</v>
       </c>
-      <c r="W12" s="10">
+      <c r="X12" s="10">
         <v>46032</v>
       </c>
-      <c r="X12" s="9" t="s">
+      <c r="Y12" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y12" s="9">
+      <c r="Z12" s="9">
         <v>98.8</v>
       </c>
-      <c r="Z12" s="9" t="s">
+      <c r="AA12" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA12" s="9" t="s">
+      <c r="AB12" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="AB12" s="9" t="s">
+      <c r="AC12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC12" s="9" t="s">
+      <c r="AD12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="AD12" s="9">
+      <c r="AE12" s="9">
         <v>6</v>
       </c>
-      <c r="AE12" s="9">
+      <c r="AF12" s="9">
         <v>2</v>
       </c>
-      <c r="AF12" s="9" t="s">
+      <c r="AG12" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="AG12" s="9" t="s">
+      <c r="AH12" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AH12" s="9" t="s">
+      <c r="AI12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI12" s="9">
+      <c r="AJ12" s="9">
         <v>0.81</v>
       </c>
-      <c r="AJ12" s="9" t="s">
+      <c r="AK12" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK12" s="9">
+      <c r="AL12" s="9">
         <v>1</v>
       </c>
-      <c r="AL12" s="9" t="s">
+      <c r="AM12" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM12" s="9" t="s">
+      <c r="AN12" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AN12" s="9" t="s">
+      <c r="AO12" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AO12" s="9" t="s">
+      <c r="AP12" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP12" s="9" t="s">
+      <c r="AQ12" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="AQ12" s="9">
+      <c r="AR12" s="9">
         <v>1260</v>
       </c>
-      <c r="AR12" s="10">
+      <c r="AS12" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="9">
+      <c r="G13" s="9">
         <v>3.5</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="I13" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="J13" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="K13" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="L13" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="L13" s="9">
+      <c r="M13" s="9">
         <v>712</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>3.54</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="O13" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="P13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P13" s="9" t="s">
+      <c r="Q13" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="Q13" s="9">
+      <c r="R13" s="9">
         <v>1412</v>
       </c>
-      <c r="R13" s="9">
+      <c r="S13" s="9">
         <v>47.8</v>
       </c>
-      <c r="S13" s="9" t="s">
+      <c r="T13" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="T13" s="9" t="s">
+      <c r="U13" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="U13" s="9" t="s">
+      <c r="V13" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="V13" s="10">
+      <c r="W13" s="10">
         <v>45301</v>
       </c>
-      <c r="W13" s="10">
+      <c r="X13" s="10">
         <v>46032</v>
       </c>
-      <c r="X13" s="9" t="s">
+      <c r="Y13" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y13" s="9">
+      <c r="Z13" s="9">
         <v>97.2</v>
       </c>
-      <c r="Z13" s="9" t="s">
+      <c r="AA13" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA13" s="9" t="s">
+      <c r="AB13" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="AB13" s="9" t="s">
+      <c r="AC13" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC13" s="9" t="s">
+      <c r="AD13" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="AD13" s="9">
+      <c r="AE13" s="9">
         <v>7</v>
       </c>
-      <c r="AE13" s="9">
+      <c r="AF13" s="9">
         <v>2</v>
       </c>
-      <c r="AF13" s="9" t="s">
+      <c r="AG13" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="AG13" s="9" t="s">
+      <c r="AH13" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AH13" s="9" t="s">
+      <c r="AI13" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI13" s="9">
+      <c r="AJ13" s="9">
         <v>0.82</v>
       </c>
-      <c r="AJ13" s="9" t="s">
+      <c r="AK13" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK13" s="9">
+      <c r="AL13" s="9">
         <v>1</v>
       </c>
-      <c r="AL13" s="9" t="s">
+      <c r="AM13" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM13" s="9" t="s">
+      <c r="AN13" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="AN13" s="9" t="s">
+      <c r="AO13" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="AO13" s="9" t="s">
+      <c r="AP13" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP13" s="9" t="s">
+      <c r="AQ13" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="AQ13" s="9" t="s">
+      <c r="AR13" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="AR13" s="10">
+      <c r="AS13" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="9">
+      <c r="G14" s="9">
         <v>3.7</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="H14" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="I14" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="J14" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="K14" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="L14" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L14" s="9">
+      <c r="M14" s="9">
         <v>713</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>3.12</v>
       </c>
-      <c r="N14" s="9" t="s">
+      <c r="O14" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O14" s="9" t="s">
+      <c r="P14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P14" s="9" t="s">
+      <c r="Q14" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="Q14" s="9">
+      <c r="R14" s="9">
         <v>1413</v>
       </c>
-      <c r="R14" s="9">
+      <c r="S14" s="9">
         <v>52.6</v>
       </c>
-      <c r="S14" s="9" t="s">
+      <c r="T14" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T14" s="9" t="s">
+      <c r="U14" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="U14" s="9" t="s">
+      <c r="V14" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="V14" s="10">
+      <c r="W14" s="10">
         <v>45301</v>
       </c>
-      <c r="W14" s="10">
+      <c r="X14" s="10">
         <v>46032</v>
       </c>
-      <c r="X14" s="9" t="s">
+      <c r="Y14" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y14" s="9">
+      <c r="Z14" s="9">
         <v>99.3</v>
       </c>
-      <c r="Z14" s="9" t="s">
+      <c r="AA14" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA14" s="9" t="s">
+      <c r="AB14" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="AB14" s="9" t="s">
+      <c r="AC14" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC14" s="9" t="s">
+      <c r="AD14" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="AD14" s="9">
+      <c r="AE14" s="9">
         <v>8</v>
       </c>
-      <c r="AE14" s="9">
+      <c r="AF14" s="9">
         <v>2</v>
       </c>
-      <c r="AF14" s="9" t="s">
+      <c r="AG14" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="AG14" s="9" t="s">
+      <c r="AH14" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AH14" s="9" t="s">
+      <c r="AI14" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI14" s="9">
+      <c r="AJ14" s="9">
         <v>0.83</v>
       </c>
-      <c r="AJ14" s="9" t="s">
+      <c r="AK14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK14" s="9">
+      <c r="AL14" s="9">
         <v>1</v>
       </c>
-      <c r="AL14" s="9" t="s">
+      <c r="AM14" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM14" s="9" t="s">
+      <c r="AN14" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="AN14" s="9" t="s">
+      <c r="AO14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AO14" s="9" t="s">
+      <c r="AP14" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP14" s="9" t="s">
+      <c r="AQ14" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AQ14" s="9" t="s">
+      <c r="AR14" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="AR14" s="10">
+      <c r="AS14" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="9">
+      <c r="G15" s="9">
         <v>3.9</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="I15" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="J15" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="K15" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="L15" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="L15" s="9">
+      <c r="M15" s="9">
         <v>714</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>1.89</v>
       </c>
-      <c r="N15" s="9" t="s">
+      <c r="O15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O15" s="9" t="s">
+      <c r="P15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P15" s="9" t="s">
+      <c r="Q15" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="Q15" s="9">
+      <c r="R15" s="9">
         <v>1414</v>
       </c>
-      <c r="R15" s="9">
+      <c r="S15" s="9">
         <v>49.1</v>
       </c>
-      <c r="S15" s="9" t="s">
+      <c r="T15" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T15" s="9" t="s">
+      <c r="U15" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="U15" s="9" t="s">
+      <c r="V15" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="V15" s="10">
+      <c r="W15" s="10">
         <v>45301</v>
       </c>
-      <c r="W15" s="10">
+      <c r="X15" s="10">
         <v>46032</v>
       </c>
-      <c r="X15" s="9" t="s">
+      <c r="Y15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y15" s="9">
+      <c r="Z15" s="9">
         <v>98.1</v>
       </c>
-      <c r="Z15" s="9" t="s">
+      <c r="AA15" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA15" s="9" t="s">
+      <c r="AB15" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="AB15" s="9" t="s">
+      <c r="AC15" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC15" s="9" t="s">
+      <c r="AD15" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AD15" s="9">
+      <c r="AE15" s="9">
         <v>9</v>
       </c>
-      <c r="AE15" s="9">
+      <c r="AF15" s="9">
         <v>2</v>
       </c>
-      <c r="AF15" s="9" t="s">
+      <c r="AG15" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="AG15" s="9" t="s">
+      <c r="AH15" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AH15" s="9" t="s">
+      <c r="AI15" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI15" s="9">
+      <c r="AJ15" s="9">
         <v>0.84</v>
       </c>
-      <c r="AJ15" s="9" t="s">
+      <c r="AK15" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK15" s="9">
+      <c r="AL15" s="9">
         <v>1</v>
       </c>
-      <c r="AL15" s="9" t="s">
+      <c r="AM15" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM15" s="9" t="s">
+      <c r="AN15" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AN15" s="9" t="s">
+      <c r="AO15" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AO15" s="9" t="s">
+      <c r="AP15" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP15" s="9" t="s">
+      <c r="AQ15" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="AQ15" s="9">
+      <c r="AR15" s="9">
         <v>1260</v>
       </c>
-      <c r="AR15" s="10">
+      <c r="AS15" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="D16" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="F16" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="9">
+      <c r="G16" s="9">
         <v>3.5</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="H16" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="I16" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="J16" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="K16" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="L16" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="L16" s="9">
+      <c r="M16" s="9">
         <v>715</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>2.57</v>
       </c>
-      <c r="N16" s="9" t="s">
+      <c r="O16" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O16" s="9" t="s">
+      <c r="P16" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P16" s="9" t="s">
+      <c r="Q16" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="Q16" s="9">
+      <c r="R16" s="9">
         <v>1415</v>
       </c>
-      <c r="R16" s="9">
+      <c r="S16" s="9">
         <v>46.3</v>
       </c>
-      <c r="S16" s="9" t="s">
+      <c r="T16" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="T16" s="9" t="s">
+      <c r="U16" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="U16" s="9" t="s">
+      <c r="V16" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="V16" s="10">
+      <c r="W16" s="10">
         <v>45301</v>
       </c>
-      <c r="W16" s="10">
+      <c r="X16" s="10">
         <v>46032</v>
       </c>
-      <c r="X16" s="9" t="s">
+      <c r="Y16" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y16" s="9">
+      <c r="Z16" s="9">
         <v>96.8</v>
       </c>
-      <c r="Z16" s="9" t="s">
+      <c r="AA16" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA16" s="9" t="s">
+      <c r="AB16" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="AB16" s="9" t="s">
+      <c r="AC16" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC16" s="9" t="s">
+      <c r="AD16" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="AD16" s="9">
+      <c r="AE16" s="9">
         <v>5</v>
       </c>
-      <c r="AE16" s="9">
+      <c r="AF16" s="9">
         <v>2</v>
       </c>
-      <c r="AF16" s="9" t="s">
+      <c r="AG16" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="AG16" s="9" t="s">
+      <c r="AH16" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AH16" s="9" t="s">
+      <c r="AI16" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI16" s="9">
+      <c r="AJ16" s="9">
         <v>0.85</v>
       </c>
-      <c r="AJ16" s="9" t="s">
+      <c r="AK16" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK16" s="9">
+      <c r="AL16" s="9">
         <v>1</v>
       </c>
-      <c r="AL16" s="9" t="s">
+      <c r="AM16" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM16" s="9" t="s">
+      <c r="AN16" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="AN16" s="9" t="s">
+      <c r="AO16" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="AO16" s="9" t="s">
+      <c r="AP16" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP16" s="9" t="s">
+      <c r="AQ16" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="AQ16" s="9" t="s">
+      <c r="AR16" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="AR16" s="10">
+      <c r="AS16" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>229</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="C17" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="9">
+      <c r="G17" s="9">
         <v>3.7</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="I17" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="J17" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="K17" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="L17" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="L17" s="9">
+      <c r="M17" s="9">
         <v>716</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>2.73</v>
       </c>
-      <c r="N17" s="9" t="s">
+      <c r="O17" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O17" s="9" t="s">
+      <c r="P17" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P17" s="9" t="s">
+      <c r="Q17" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="Q17" s="9">
+      <c r="R17" s="9">
         <v>1416</v>
       </c>
-      <c r="R17" s="9">
+      <c r="S17" s="9">
         <v>50.7</v>
       </c>
-      <c r="S17" s="9" t="s">
+      <c r="T17" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T17" s="9" t="s">
+      <c r="U17" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="U17" s="9" t="s">
+      <c r="V17" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="V17" s="10">
+      <c r="W17" s="10">
         <v>45301</v>
       </c>
-      <c r="W17" s="10">
+      <c r="X17" s="10">
         <v>46032</v>
       </c>
-      <c r="X17" s="9" t="s">
+      <c r="Y17" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y17" s="9">
+      <c r="Z17" s="9">
         <v>97.6</v>
       </c>
-      <c r="Z17" s="9" t="s">
+      <c r="AA17" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA17" s="9" t="s">
+      <c r="AB17" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="AB17" s="9" t="s">
+      <c r="AC17" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC17" s="9" t="s">
+      <c r="AD17" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="AD17" s="9">
+      <c r="AE17" s="9">
         <v>6</v>
       </c>
-      <c r="AE17" s="9">
+      <c r="AF17" s="9">
         <v>2</v>
       </c>
-      <c r="AF17" s="9" t="s">
+      <c r="AG17" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="AG17" s="9" t="s">
+      <c r="AH17" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AH17" s="9" t="s">
+      <c r="AI17" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI17" s="9">
+      <c r="AJ17" s="9">
         <v>0.86</v>
       </c>
-      <c r="AJ17" s="9" t="s">
+      <c r="AK17" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK17" s="9">
+      <c r="AL17" s="9">
         <v>1</v>
       </c>
-      <c r="AL17" s="9" t="s">
+      <c r="AM17" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM17" s="9" t="s">
+      <c r="AN17" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="AN17" s="9" t="s">
+      <c r="AO17" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AO17" s="9" t="s">
+      <c r="AP17" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP17" s="9" t="s">
+      <c r="AQ17" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AQ17" s="9" t="s">
+      <c r="AR17" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="AR17" s="10">
+      <c r="AS17" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="D18" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="E18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="F18" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="9">
+      <c r="G18" s="9">
         <v>3.9</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="H18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="I18" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="J18" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="K18" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="L18" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="L18" s="9">
+      <c r="M18" s="9">
         <v>717</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>2.66</v>
       </c>
-      <c r="N18" s="9" t="s">
+      <c r="O18" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O18" s="9" t="s">
+      <c r="P18" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P18" s="9" t="s">
+      <c r="Q18" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="Q18" s="9">
+      <c r="R18" s="9">
         <v>1417</v>
       </c>
-      <c r="R18" s="9">
+      <c r="S18" s="9">
         <v>53.5</v>
       </c>
-      <c r="S18" s="9" t="s">
+      <c r="T18" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T18" s="9" t="s">
+      <c r="U18" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="U18" s="9" t="s">
+      <c r="V18" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="V18" s="10">
+      <c r="W18" s="10">
         <v>45301</v>
       </c>
-      <c r="W18" s="10">
+      <c r="X18" s="10">
         <v>46032</v>
       </c>
-      <c r="X18" s="9" t="s">
+      <c r="Y18" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y18" s="9">
+      <c r="Z18" s="9">
         <v>98.9</v>
       </c>
-      <c r="Z18" s="9" t="s">
+      <c r="AA18" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA18" s="9" t="s">
+      <c r="AB18" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="AB18" s="9" t="s">
+      <c r="AC18" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC18" s="9" t="s">
+      <c r="AD18" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="AD18" s="9">
+      <c r="AE18" s="9">
         <v>7</v>
       </c>
-      <c r="AE18" s="9">
+      <c r="AF18" s="9">
         <v>2</v>
       </c>
-      <c r="AF18" s="9" t="s">
+      <c r="AG18" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="AG18" s="9" t="s">
+      <c r="AH18" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AH18" s="9" t="s">
+      <c r="AI18" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI18" s="9">
+      <c r="AJ18" s="9">
         <v>0.87</v>
       </c>
-      <c r="AJ18" s="9" t="s">
+      <c r="AK18" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK18" s="9">
+      <c r="AL18" s="9">
         <v>1</v>
       </c>
-      <c r="AL18" s="9" t="s">
+      <c r="AM18" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM18" s="9" t="s">
+      <c r="AN18" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AN18" s="9" t="s">
+      <c r="AO18" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AO18" s="9" t="s">
+      <c r="AP18" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP18" s="9" t="s">
+      <c r="AQ18" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="AQ18" s="9">
+      <c r="AR18" s="9">
         <v>1260</v>
       </c>
-      <c r="AR18" s="10">
+      <c r="AS18" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="C19" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="D19" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="E19" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F19" s="9">
+      <c r="G19" s="9">
         <v>3.5</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="H19" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="I19" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="J19" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="K19" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="L19" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="L19" s="9">
+      <c r="M19" s="9">
         <v>718</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>3.43</v>
       </c>
-      <c r="N19" s="9" t="s">
+      <c r="O19" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O19" s="9" t="s">
+      <c r="P19" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P19" s="9" t="s">
+      <c r="Q19" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="Q19" s="9">
+      <c r="R19" s="9">
         <v>1418</v>
       </c>
-      <c r="R19" s="9">
+      <c r="S19" s="9">
         <v>48.9</v>
       </c>
-      <c r="S19" s="9" t="s">
+      <c r="T19" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="T19" s="9" t="s">
+      <c r="U19" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="U19" s="9" t="s">
+      <c r="V19" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="V19" s="10">
+      <c r="W19" s="10">
         <v>45301</v>
       </c>
-      <c r="W19" s="10">
+      <c r="X19" s="10">
         <v>46032</v>
       </c>
-      <c r="X19" s="9" t="s">
+      <c r="Y19" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y19" s="9">
+      <c r="Z19" s="9">
         <v>97.3</v>
       </c>
-      <c r="Z19" s="9" t="s">
+      <c r="AA19" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA19" s="9" t="s">
+      <c r="AB19" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="AB19" s="9" t="s">
+      <c r="AC19" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC19" s="9" t="s">
+      <c r="AD19" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="AD19" s="9">
+      <c r="AE19" s="9">
         <v>8</v>
       </c>
-      <c r="AE19" s="9">
+      <c r="AF19" s="9">
         <v>2</v>
       </c>
-      <c r="AF19" s="9" t="s">
+      <c r="AG19" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="AG19" s="9" t="s">
+      <c r="AH19" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AH19" s="9" t="s">
+      <c r="AI19" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI19" s="9">
+      <c r="AJ19" s="9">
         <v>0.88</v>
       </c>
-      <c r="AJ19" s="9" t="s">
+      <c r="AK19" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK19" s="9">
+      <c r="AL19" s="9">
         <v>1</v>
       </c>
-      <c r="AL19" s="9" t="s">
+      <c r="AM19" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM19" s="9" t="s">
+      <c r="AN19" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="AN19" s="9" t="s">
+      <c r="AO19" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="AO19" s="9" t="s">
+      <c r="AP19" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP19" s="9" t="s">
+      <c r="AQ19" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="AQ19" s="9" t="s">
+      <c r="AR19" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="AR19" s="10">
+      <c r="AS19" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>229</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="D20" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="E20" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="F20" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="9">
+      <c r="G20" s="9">
         <v>3.7</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="H20" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="I20" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="J20" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="K20" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="L20" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="L20" s="9">
+      <c r="M20" s="9">
         <v>719</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>3.08</v>
       </c>
-      <c r="N20" s="9" t="s">
+      <c r="O20" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O20" s="9" t="s">
+      <c r="P20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P20" s="9" t="s">
+      <c r="Q20" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="Q20" s="9">
+      <c r="R20" s="9">
         <v>1419</v>
       </c>
-      <c r="R20" s="9">
+      <c r="S20" s="9">
         <v>47.2</v>
       </c>
-      <c r="S20" s="9" t="s">
+      <c r="T20" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T20" s="9" t="s">
+      <c r="U20" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="U20" s="9" t="s">
+      <c r="V20" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="V20" s="10">
+      <c r="W20" s="10">
         <v>45301</v>
       </c>
-      <c r="W20" s="10">
+      <c r="X20" s="10">
         <v>46032</v>
       </c>
-      <c r="X20" s="9" t="s">
+      <c r="Y20" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y20" s="9">
+      <c r="Z20" s="9">
         <v>96.7</v>
       </c>
-      <c r="Z20" s="9" t="s">
+      <c r="AA20" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA20" s="9" t="s">
+      <c r="AB20" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="AB20" s="9" t="s">
+      <c r="AC20" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC20" s="9" t="s">
+      <c r="AD20" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="AD20" s="9">
+      <c r="AE20" s="9">
         <v>9</v>
       </c>
-      <c r="AE20" s="9">
+      <c r="AF20" s="9">
         <v>2</v>
       </c>
-      <c r="AF20" s="9" t="s">
+      <c r="AG20" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="AG20" s="9" t="s">
+      <c r="AH20" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AH20" s="9" t="s">
+      <c r="AI20" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI20" s="9">
+      <c r="AJ20" s="9">
         <v>0.89</v>
       </c>
-      <c r="AJ20" s="9" t="s">
+      <c r="AK20" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK20" s="9">
+      <c r="AL20" s="9">
         <v>1</v>
       </c>
-      <c r="AL20" s="9" t="s">
+      <c r="AM20" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM20" s="9" t="s">
+      <c r="AN20" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="AN20" s="9" t="s">
+      <c r="AO20" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AO20" s="9" t="s">
+      <c r="AP20" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP20" s="9" t="s">
+      <c r="AQ20" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="AQ20" s="9" t="s">
+      <c r="AR20" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="AR20" s="10">
+      <c r="AS20" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>229</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="C21" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="E21" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F21" s="9">
+      <c r="G21" s="9">
         <v>3.9</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="H21" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="I21" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="J21" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="K21" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="K21" s="9" t="s">
+      <c r="L21" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="L21" s="9">
+      <c r="M21" s="9">
         <v>720</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>1.96</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="O21" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="O21" s="9" t="s">
+      <c r="P21" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="P21" s="9" t="s">
+      <c r="Q21" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="Q21" s="9">
+      <c r="R21" s="9">
         <v>1420</v>
       </c>
-      <c r="R21" s="9">
+      <c r="S21" s="9">
         <v>51.8</v>
       </c>
-      <c r="S21" s="9" t="s">
+      <c r="T21" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T21" s="9" t="s">
+      <c r="U21" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="U21" s="9" t="s">
+      <c r="V21" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="V21" s="10">
+      <c r="W21" s="10">
         <v>45301</v>
       </c>
-      <c r="W21" s="10">
+      <c r="X21" s="10">
         <v>46032</v>
       </c>
-      <c r="X21" s="9" t="s">
+      <c r="Y21" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="Y21" s="9">
+      <c r="Z21" s="9">
         <v>98.4</v>
       </c>
-      <c r="Z21" s="9" t="s">
+      <c r="AA21" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AA21" s="9" t="s">
+      <c r="AB21" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="AB21" s="9" t="s">
+      <c r="AC21" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AC21" s="9" t="s">
+      <c r="AD21" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="AD21" s="9">
+      <c r="AE21" s="9">
         <v>5</v>
       </c>
-      <c r="AE21" s="9">
+      <c r="AF21" s="9">
         <v>2</v>
       </c>
-      <c r="AF21" s="9" t="s">
+      <c r="AG21" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="AG21" s="9" t="s">
+      <c r="AH21" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AH21" s="9" t="s">
+      <c r="AI21" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AI21" s="9">
+      <c r="AJ21" s="9">
         <v>0.9</v>
       </c>
-      <c r="AJ21" s="9" t="s">
+      <c r="AK21" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AK21" s="9">
+      <c r="AL21" s="9">
         <v>1</v>
       </c>
-      <c r="AL21" s="9" t="s">
+      <c r="AM21" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM21" s="9" t="s">
+      <c r="AN21" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AN21" s="9" t="s">
+      <c r="AO21" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AO21" s="9" t="s">
+      <c r="AP21" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="AP21" s="9" t="s">
+      <c r="AQ21" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="AQ21" s="9">
+      <c r="AR21" s="9">
         <v>1260</v>
       </c>
-      <c r="AR21" s="10">
+      <c r="AS21" s="10">
         <v>45658</v>
       </c>
     </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="F24" s="9"/>
+    <row r="24" spans="1:45" x14ac:dyDescent="0.35">
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
     </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="F25" s="9"/>
+    <row r="25" spans="1:45" x14ac:dyDescent="0.35">
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
     </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="F26" s="9"/>
-      <c r="G26" s="11" t="s">
+    <row r="26" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="G26" s="9"/>
+      <c r="H26" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="9"/>
+      <c r="I26" s="2"/>
       <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
     </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="F27" s="9"/>
-      <c r="G27" s="11" t="s">
+    <row r="27" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="G27" s="9"/>
+      <c r="H27" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="9"/>
+      <c r="I27" s="4"/>
       <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
     </row>
-    <row r="28" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="F28" s="9"/>
-      <c r="G28" s="11" t="s">
+    <row r="28" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="G28" s="9"/>
+      <c r="H28" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="9"/>
+      <c r="I28" s="5"/>
       <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="F29" s="9"/>
-      <c r="G29" s="11" t="s">
+    <row r="29" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="G29" s="9"/>
+      <c r="H29" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="H29" s="6"/>
-      <c r="I29" s="9"/>
+      <c r="I29" s="6"/>
       <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
     </row>
-    <row r="30" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="F30" s="9"/>
-      <c r="G30" s="11" t="s">
+    <row r="30" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="G30" s="9"/>
+      <c r="H30" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="H30" s="7"/>
-      <c r="I30" s="9"/>
+      <c r="I30" s="7"/>
       <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
     </row>
-    <row r="31" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="F31" s="9"/>
-      <c r="G31" s="11" t="s">
+    <row r="31" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="G31" s="9"/>
+      <c r="H31" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="H31" s="8"/>
-      <c r="I31" s="9"/>
+      <c r="I31" s="8"/>
       <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
     </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.35">
-      <c r="G32" s="11" t="s">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.35">
+      <c r="H32" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
